--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/23,09,26 Останкино СЫРЫ/дв 23,09,26 днрсч ост сыр.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/23,09,26 Останкино СЫРЫ/дв 23,09,26 днрсч ост сыр.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\09,26\23,09,26 Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF9840A-9180-4B40-9F3A-297F44FB2AAF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F0FA288-F120-4E3E-87EE-07F2D8C1B05A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="102">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -159,9 +159,6 @@
   </si>
   <si>
     <t>4421577 Спред растительно-сливочный "Сливочный вкус" 82,5% 180гр  Останкино</t>
-  </si>
-  <si>
-    <t>17,09,26 - нет на заводе / 10,09,26 - нет на заводе / 03,09,26 - нет на заводе / 27,08,26 - нет на заводе / 24,08,26 - нет на заводе / 13,08,26 - нет на заводе / 30,07,26 - нет на заводе / 62шт в уценку (28,07,26)</t>
   </si>
   <si>
     <t>4421584 Спред растительно-сливочный "Сливочный вкус" 72,5% 180гр  Останкино</t>
@@ -343,6 +340,9 @@
   <si>
     <t>итого1</t>
   </si>
+  <si>
+    <t>24,09,26 - нет на заводе / 17,09,26 - нет на заводе / 10,09,26 - нет на заводе / 03,09,26 - нет на заводе / 27,08,26 - нет на заводе / 24,08,26 - нет на заводе / 13,08,26 - нет на заводе / 30,07,26 - нет на заводе / 62шт в уценку (28,07,26)</t>
+  </si>
 </sst>
 </file>
 
@@ -389,7 +389,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -409,6 +409,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -448,7 +454,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -464,6 +470,7 @@
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -2690,22 +2697,22 @@
         <v>16</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="T3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="U3" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="U3" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="V3" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X3" s="2" t="s">
         <v>17</v>
@@ -2791,19 +2798,19 @@
       </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="T4" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="U4" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="T4" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="V4" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
@@ -2840,10 +2847,10 @@
       </c>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AL4" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="AL4" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="AM4" s="1"/>
       <c r="AN4" s="1"/>
@@ -2912,7 +2919,7 @@
       </c>
       <c r="S5" s="4">
         <f t="shared" si="0"/>
-        <v>3124</v>
+        <v>3100</v>
       </c>
       <c r="T5" s="4">
         <f t="shared" si="0"/>
@@ -3084,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AJ6" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AK6" s="1">
         <f>G6*R6</f>
@@ -3200,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="AJ7" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AK7" s="1">
         <f t="shared" ref="AK7:AK47" si="8">G7*R7</f>
@@ -3516,9 +3523,8 @@
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="S10" s="5">
-        <f>VLOOKUP(A10,филиал!A:B,2,0)</f>
-        <v>12</v>
+      <c r="S10" s="15">
+        <v>0</v>
       </c>
       <c r="T10" s="5"/>
       <c r="U10" s="5"/>
@@ -3563,7 +3569,7 @@
         <v>2</v>
       </c>
       <c r="AJ10" s="1" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="AK10" s="1">
         <f t="shared" si="8"/>
@@ -3591,7 +3597,7 @@
     </row>
     <row r="11" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>35</v>
@@ -3631,9 +3637,8 @@
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="S11" s="5">
-        <f>VLOOKUP(A11,филиал!A:B,2,0)</f>
-        <v>12</v>
+      <c r="S11" s="15">
+        <v>0</v>
       </c>
       <c r="T11" s="5"/>
       <c r="U11" s="5"/>
@@ -3678,7 +3683,7 @@
         <v>1.2</v>
       </c>
       <c r="AJ11" s="1" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="AK11" s="1">
         <f t="shared" si="8"/>
@@ -3706,7 +3711,7 @@
     </row>
     <row r="12" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>39</v>
@@ -3750,7 +3755,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S12" s="5"/>
+      <c r="S12" s="15"/>
       <c r="T12" s="5"/>
       <c r="U12" s="5"/>
       <c r="V12" s="13"/>
@@ -3820,7 +3825,7 @@
     </row>
     <row r="13" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>35</v>
@@ -3904,7 +3909,7 @@
         <v>0</v>
       </c>
       <c r="AJ13" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AK13" s="1">
         <f t="shared" si="8"/>
@@ -3932,7 +3937,7 @@
     </row>
     <row r="14" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>35</v>
@@ -3990,7 +3995,7 @@
         <v>250</v>
       </c>
       <c r="W14" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X14" s="1">
         <f t="shared" si="6"/>
@@ -4057,7 +4062,7 @@
     </row>
     <row r="15" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>35</v>
@@ -4152,7 +4157,7 @@
         <v>4</v>
       </c>
       <c r="AJ15" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK15" s="1">
         <f t="shared" si="8"/>
@@ -4180,7 +4185,7 @@
     </row>
     <row r="16" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>35</v>
@@ -4238,7 +4243,7 @@
         <v>200</v>
       </c>
       <c r="W16" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X16" s="1">
         <f t="shared" si="6"/>
@@ -4305,7 +4310,7 @@
     </row>
     <row r="17" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>35</v>
@@ -4400,7 +4405,7 @@
         <v>6.2</v>
       </c>
       <c r="AJ17" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AK17" s="1">
         <f t="shared" si="8"/>
@@ -4428,7 +4433,7 @@
     </row>
     <row r="18" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>35</v>
@@ -4549,7 +4554,7 @@
     </row>
     <row r="19" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>35</v>
@@ -4670,7 +4675,7 @@
     </row>
     <row r="20" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>35</v>
@@ -4794,7 +4799,7 @@
     </row>
     <row r="21" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>35</v>
@@ -4918,7 +4923,7 @@
     </row>
     <row r="22" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>35</v>
@@ -5007,7 +5012,7 @@
         <v>0.4</v>
       </c>
       <c r="AJ22" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AK22" s="1">
         <f t="shared" si="8"/>
@@ -5035,7 +5040,7 @@
     </row>
     <row r="23" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>35</v>
@@ -5151,7 +5156,7 @@
     </row>
     <row r="24" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>35</v>
@@ -5267,7 +5272,7 @@
     </row>
     <row r="25" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>35</v>
@@ -5360,7 +5365,7 @@
         <v>20.8</v>
       </c>
       <c r="AJ25" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AK25" s="1">
         <f t="shared" si="8"/>
@@ -5388,7 +5393,7 @@
     </row>
     <row r="26" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>35</v>
@@ -5510,7 +5515,7 @@
     </row>
     <row r="27" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>35</v>
@@ -5632,7 +5637,7 @@
     </row>
     <row r="28" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>35</v>
@@ -5722,7 +5727,7 @@
         <v>11.2</v>
       </c>
       <c r="AJ28" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AK28" s="1">
         <f t="shared" si="8"/>
@@ -5750,7 +5755,7 @@
     </row>
     <row r="29" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>35</v>
@@ -5846,7 +5851,7 @@
         <v>58.4</v>
       </c>
       <c r="AJ29" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AK29" s="1">
         <f t="shared" si="8"/>
@@ -5874,7 +5879,7 @@
     </row>
     <row r="30" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>35</v>
@@ -5965,7 +5970,7 @@
         <v>5.6</v>
       </c>
       <c r="AJ30" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AK30" s="1">
         <f t="shared" si="8"/>
@@ -5993,7 +5998,7 @@
     </row>
     <row r="31" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>35</v>
@@ -6087,7 +6092,7 @@
         <v>3.2</v>
       </c>
       <c r="AJ31" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AK31" s="1">
         <f t="shared" si="8"/>
@@ -6115,7 +6120,7 @@
     </row>
     <row r="32" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>35</v>
@@ -6237,7 +6242,7 @@
     </row>
     <row r="33" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>35</v>
@@ -6293,7 +6298,7 @@
         <v>200</v>
       </c>
       <c r="W33" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X33" s="1">
         <f t="shared" si="6"/>
@@ -6334,7 +6339,7 @@
         <v>11.8</v>
       </c>
       <c r="AJ33" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AK33" s="1">
         <f t="shared" si="8"/>
@@ -6362,7 +6367,7 @@
     </row>
     <row r="34" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>35</v>
@@ -6476,7 +6481,7 @@
     </row>
     <row r="35" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>35</v>
@@ -6592,7 +6597,7 @@
     </row>
     <row r="36" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>39</v>
@@ -6716,7 +6721,7 @@
     </row>
     <row r="37" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>39</v>
@@ -6812,7 +6817,7 @@
         <v>2.0184000000000002</v>
       </c>
       <c r="AJ37" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AK37" s="1">
         <f t="shared" si="8"/>
@@ -6840,7 +6845,7 @@
     </row>
     <row r="38" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>39</v>
@@ -6961,7 +6966,7 @@
     </row>
     <row r="39" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>39</v>
@@ -7052,7 +7057,7 @@
         <v>0</v>
       </c>
       <c r="AJ39" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AK39" s="1">
         <f t="shared" si="8"/>
@@ -7080,7 +7085,7 @@
     </row>
     <row r="40" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>35</v>
@@ -7201,7 +7206,7 @@
     </row>
     <row r="41" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>35</v>
@@ -7325,7 +7330,7 @@
     </row>
     <row r="42" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>39</v>
@@ -7419,7 +7424,7 @@
         <v>3.5344000000000002</v>
       </c>
       <c r="AJ42" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK42" s="1">
         <f t="shared" si="8"/>
@@ -7447,7 +7452,7 @@
     </row>
     <row r="43" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>35</v>
@@ -7563,7 +7568,7 @@
     </row>
     <row r="44" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>35</v>
@@ -7684,7 +7689,7 @@
     </row>
     <row r="45" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>39</v>
@@ -7779,7 +7784,7 @@
         <v>0.58240000000000003</v>
       </c>
       <c r="AJ45" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AK45" s="1">
         <f t="shared" si="8"/>
@@ -7807,7 +7812,7 @@
     </row>
     <row r="46" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>35</v>
@@ -7929,7 +7934,7 @@
     </row>
     <row r="47" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>39</v>
@@ -32943,7 +32948,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4">
         <v>12</v>
@@ -32951,7 +32956,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5">
         <v>36</v>
@@ -32959,7 +32964,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B6">
         <v>48</v>
@@ -32967,7 +32972,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B7">
         <v>16</v>
@@ -32975,7 +32980,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8">
         <v>16</v>
@@ -32983,7 +32988,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B9">
         <v>270</v>
@@ -32991,7 +32996,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B10">
         <v>200</v>
@@ -32999,7 +33004,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B11">
         <v>16</v>
@@ -33007,7 +33012,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B12">
         <v>40</v>
@@ -33015,7 +33020,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13">
         <v>168</v>
@@ -33023,7 +33028,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B14">
         <v>152</v>
@@ -33031,7 +33036,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B15">
         <v>450</v>
@@ -33039,7 +33044,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B16">
         <v>40</v>
@@ -33047,7 +33052,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B17">
         <v>30</v>
@@ -33055,7 +33060,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B18">
         <v>870</v>
@@ -33063,7 +33068,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B19">
         <v>16</v>
@@ -33071,7 +33076,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B20">
         <v>33</v>
@@ -33079,7 +33084,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B21">
         <v>16</v>
@@ -33087,7 +33092,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B22">
         <v>12</v>
@@ -33095,7 +33100,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B23">
         <v>450</v>
@@ -33103,7 +33108,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B24">
         <v>12</v>
@@ -33111,7 +33116,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B25">
         <v>30</v>
@@ -33119,7 +33124,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B26">
         <v>30</v>
@@ -33127,7 +33132,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B27">
         <v>20</v>
@@ -33135,7 +33140,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B28">
         <v>45</v>
@@ -33153,7 +33158,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B1">
         <v>252</v>
@@ -33161,7 +33166,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2">
         <v>204</v>
@@ -33169,7 +33174,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B3">
         <v>200</v>
